--- a/Maps/KeyBinds.xlsx
+++ b/Maps/KeyBinds.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Den\OneDrive\Personal\Thrustmaster\TARGET\Clicker\Development\ED_TargetScript-503\Maps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A579D10-CAFC-4242-8897-E50E94DD5DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF099212-D4ED-4BF0-84E4-E71405A9D37B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2970" yWindow="660" windowWidth="28305" windowHeight="18765" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="690" yWindow="225" windowWidth="33450" windowHeight="18765" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="In Ship" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="306">
   <si>
     <t>R-CTRL</t>
   </si>
@@ -929,6 +929,21 @@
   </si>
   <si>
     <t>Standard Unmodified Keys - v503</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>End</t>
+  </si>
+  <si>
+    <t>Reset Mouse</t>
+  </si>
+  <si>
+    <t>Toggle Relative Mouse</t>
+  </si>
+  <si>
+    <t>???</t>
   </si>
 </sst>
 </file>
@@ -952,7 +967,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -977,6 +992,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="19">
     <border>
@@ -1232,7 +1253,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1258,9 +1279,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1356,6 +1374,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1662,68 +1686,70 @@
   <sheetData>
     <row r="1" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="35" t="s">
         <v>300</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="38"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="37"/>
     </row>
     <row r="3" spans="2:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="16" t="s">
         <v>168</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="16" t="s">
         <v>171</v>
       </c>
       <c r="F3" s="2">
         <v>6</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="I3" s="16" t="s">
         <v>163</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="L3" s="13" t="s">
+      <c r="L3" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="M3" s="3"/>
+      <c r="M3" s="3" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="17" t="s">
         <v>209</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="17" t="s">
         <v>119</v>
       </c>
       <c r="F4" s="4">
@@ -1733,17 +1759,17 @@
       <c r="H4" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="17" t="s">
         <v>128</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>95</v>
       </c>
       <c r="K4" s="5"/>
-      <c r="L4" s="13" t="s">
+      <c r="L4" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="M4" s="17" t="s">
+      <c r="M4" s="16" t="s">
         <v>208</v>
       </c>
     </row>
@@ -1751,37 +1777,37 @@
       <c r="B5" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="17" t="s">
         <v>210</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="17" t="s">
         <v>144</v>
       </c>
       <c r="F5" s="4">
         <v>8</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="17" t="s">
         <v>158</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="I5" s="17" t="s">
         <v>176</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="K5" s="18" t="s">
+      <c r="K5" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="L5" s="14" t="s">
+      <c r="L5" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="M5" s="18" t="s">
+      <c r="M5" s="17" t="s">
         <v>135</v>
       </c>
     </row>
@@ -1789,37 +1815,37 @@
       <c r="B6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="17" t="s">
         <v>190</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="17" t="s">
         <v>122</v>
       </c>
       <c r="F6" s="4">
         <v>9</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="17" t="s">
         <v>159</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="I6" s="18" t="s">
+      <c r="I6" s="17" t="s">
         <v>177</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="K6" s="18" t="s">
+      <c r="K6" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="L6" s="14" t="s">
+      <c r="L6" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="M6" s="18" t="s">
+      <c r="M6" s="17" t="s">
         <v>142</v>
       </c>
     </row>
@@ -1827,37 +1853,37 @@
       <c r="B7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="17" t="s">
         <v>170</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="17" t="s">
         <v>123</v>
       </c>
       <c r="F7" s="4">
         <v>0</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="17" t="s">
         <v>160</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I7" s="18" t="s">
+      <c r="I7" s="17" t="s">
         <v>178</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="K7" s="18" t="s">
+      <c r="K7" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="L7" s="14" t="s">
+      <c r="L7" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="M7" s="18" t="s">
+      <c r="M7" s="17" t="s">
         <v>156</v>
       </c>
     </row>
@@ -1865,37 +1891,37 @@
       <c r="B8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="17" t="s">
         <v>145</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="17" t="s">
         <v>132</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="17" t="s">
         <v>133</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="I8" s="18" t="s">
+      <c r="I8" s="17" t="s">
         <v>179</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="K8" s="18" t="s">
+      <c r="K8" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="L8" s="14" t="s">
+      <c r="L8" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="M8" s="18" t="s">
+      <c r="M8" s="17" t="s">
         <v>118</v>
       </c>
     </row>
@@ -1903,47 +1929,47 @@
       <c r="B9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="17" t="s">
         <v>148</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="17" t="s">
         <v>143</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="17" t="s">
         <v>165</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="I9" s="17" t="s">
         <v>180</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="K9" s="18" t="s">
+      <c r="K9" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="L9" s="14"/>
+      <c r="L9" s="13"/>
       <c r="M9" s="5"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="17" t="s">
         <v>149</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="17" t="s">
         <v>117</v>
       </c>
       <c r="F10" s="4" t="s">
@@ -1953,19 +1979,19 @@
       <c r="H10" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="I10" s="18" t="s">
+      <c r="I10" s="17" t="s">
         <v>181</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="K10" s="18" t="s">
+      <c r="K10" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="L10" s="14" t="s">
+      <c r="L10" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="M10" s="18" t="s">
+      <c r="M10" s="17" t="s">
         <v>166</v>
       </c>
     </row>
@@ -1973,13 +1999,13 @@
       <c r="B11" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="17" t="s">
         <v>153</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="17" t="s">
         <v>147</v>
       </c>
       <c r="F11" s="4" t="s">
@@ -1989,19 +2015,19 @@
       <c r="H11" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="I11" s="18" t="s">
+      <c r="I11" s="17" t="s">
         <v>182</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="K11" s="18" t="s">
+      <c r="K11" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="L11" s="14" t="s">
+      <c r="L11" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="M11" s="18" t="s">
+      <c r="M11" s="17" t="s">
         <v>167</v>
       </c>
     </row>
@@ -2009,35 +2035,35 @@
       <c r="B12" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="17" t="s">
         <v>155</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="17" t="s">
         <v>121</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="17" t="s">
         <v>197</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="I12" s="18" t="s">
+      <c r="I12" s="17" t="s">
         <v>183</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>103</v>
       </c>
       <c r="K12" s="5"/>
-      <c r="L12" s="14" t="s">
+      <c r="L12" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="M12" s="18" t="s">
+      <c r="M12" s="17" t="s">
         <v>168</v>
       </c>
     </row>
@@ -2045,37 +2071,37 @@
       <c r="B13" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="17" t="s">
         <v>154</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="17" t="s">
         <v>191</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="G13" s="18" t="s">
+      <c r="G13" s="17" t="s">
         <v>198</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I13" s="18" t="s">
+      <c r="I13" s="17" t="s">
         <v>184</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="K13" s="18" t="s">
+      <c r="K13" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="L13" s="14" t="s">
+      <c r="L13" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="M13" s="18" t="s">
+      <c r="M13" s="17" t="s">
         <v>169</v>
       </c>
     </row>
@@ -2083,19 +2109,19 @@
       <c r="B14" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="17" t="s">
         <v>186</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="17" t="s">
         <v>125</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="G14" s="18" t="s">
+      <c r="G14" s="17" t="s">
         <v>134</v>
       </c>
       <c r="H14" s="4" t="s">
@@ -2105,29 +2131,29 @@
       <c r="J14" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="K14" s="24" t="s">
+      <c r="K14" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="L14" s="14"/>
+      <c r="L14" s="13"/>
       <c r="M14" s="5"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="17" t="s">
         <v>157</v>
       </c>
       <c r="D15" s="4">
         <v>2</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="17" t="s">
         <v>124</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="18" t="s">
+      <c r="G15" s="17" t="s">
         <v>199</v>
       </c>
       <c r="H15" s="4" t="s">
@@ -2137,13 +2163,13 @@
       <c r="J15" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="K15" s="18" t="s">
+      <c r="K15" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="L15" s="14" t="s">
+      <c r="L15" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="M15" s="18" t="s">
+      <c r="M15" s="17" t="s">
         <v>173</v>
       </c>
     </row>
@@ -2151,87 +2177,87 @@
       <c r="B16" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="17" t="s">
         <v>150</v>
       </c>
       <c r="D16" s="4">
         <v>3</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="17" t="s">
         <v>126</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="G16" s="17" t="s">
         <v>131</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="I16" s="24" t="s">
+      <c r="I16" s="23" t="s">
         <v>116</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="K16" s="18" t="s">
+      <c r="K16" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="L16" s="14"/>
+      <c r="L16" s="13"/>
       <c r="M16" s="5"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="17" t="s">
         <v>130</v>
       </c>
       <c r="D17" s="4">
         <v>4</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="17" t="s">
         <v>127</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="G17" s="18" t="s">
+      <c r="G17" s="17" t="s">
         <v>151</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="I17" s="18" t="s">
+      <c r="I17" s="17" t="s">
         <v>185</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="K17" s="18" t="s">
+      <c r="K17" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="L17" s="14"/>
+      <c r="L17" s="13"/>
       <c r="M17" s="5"/>
     </row>
     <row r="18" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="18" t="s">
         <v>189</v>
       </c>
       <c r="D18" s="6">
         <v>5</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="18" t="s">
         <v>161</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="G18" s="19" t="s">
+      <c r="G18" s="18" t="s">
         <v>152</v>
       </c>
       <c r="H18" s="6" t="s">
@@ -2241,38 +2267,38 @@
       <c r="J18" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="K18" s="19" t="s">
+      <c r="K18" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="L18" s="15"/>
+      <c r="L18" s="14"/>
       <c r="M18" s="7"/>
     </row>
     <row r="19" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C20" s="40"/>
-      <c r="D20" s="39" t="s">
+      <c r="C20" s="39"/>
+      <c r="D20" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="40"/>
-      <c r="F20" s="39" t="s">
+      <c r="E20" s="39"/>
+      <c r="F20" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="G20" s="40"/>
-      <c r="H20" s="39" t="s">
+      <c r="G20" s="39"/>
+      <c r="H20" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="I20" s="40"/>
-      <c r="J20" s="39" t="s">
+      <c r="I20" s="39"/>
+      <c r="J20" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="40"/>
-      <c r="L20" s="39" t="s">
+      <c r="K20" s="39"/>
+      <c r="L20" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="M20" s="40"/>
+      <c r="M20" s="39"/>
       <c r="N20"/>
       <c r="O20"/>
     </row>
@@ -2282,13 +2308,13 @@
       <c r="D21" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E21" s="17" t="s">
+      <c r="E21" s="16" t="s">
         <v>44</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G21" s="17" t="s">
+      <c r="G21" s="16" t="s">
         <v>21</v>
       </c>
       <c r="H21" s="2"/>
@@ -2302,19 +2328,19 @@
       <c r="B22" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="17" t="s">
         <v>193</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="17" t="s">
         <v>211</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G22" s="18" t="s">
+      <c r="G22" s="17" t="s">
         <v>200</v>
       </c>
       <c r="H22" s="4"/>
@@ -2328,19 +2354,19 @@
       <c r="B23" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="17" t="s">
         <v>194</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="E23" s="17" t="s">
         <v>46</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G23" s="18" t="s">
+      <c r="G23" s="17" t="s">
         <v>201</v>
       </c>
       <c r="H23" s="4"/>
@@ -2355,13 +2381,13 @@
       <c r="D24" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="17" t="s">
         <v>47</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G24" s="18" t="s">
+      <c r="G24" s="17" t="s">
         <v>202</v>
       </c>
       <c r="H24" s="4"/>
@@ -2377,13 +2403,13 @@
       <c r="D25" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E25" s="18" t="s">
+      <c r="E25" s="17" t="s">
         <v>48</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G25" s="18" t="s">
+      <c r="G25" s="17" t="s">
         <v>203</v>
       </c>
       <c r="H25" s="4"/>
@@ -2399,13 +2425,13 @@
       <c r="D26" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="17" t="s">
         <v>50</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="18" t="s">
+      <c r="G26" s="17" t="s">
         <v>212</v>
       </c>
       <c r="H26" s="4"/>
@@ -2421,13 +2447,13 @@
       <c r="D27" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="17" t="s">
         <v>51</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G27" s="18" t="s">
+      <c r="G27" s="17" t="s">
         <v>213</v>
       </c>
       <c r="H27" s="4"/>
@@ -2442,13 +2468,13 @@
       <c r="D28" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="17" t="s">
         <v>52</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G28" s="18" t="s">
+      <c r="G28" s="17" t="s">
         <v>26</v>
       </c>
       <c r="H28" s="4"/>
@@ -2464,13 +2490,13 @@
       <c r="D29" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E29" s="18" t="s">
+      <c r="E29" s="17" t="s">
         <v>63</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G29" s="18" t="s">
+      <c r="G29" s="17" t="s">
         <v>28</v>
       </c>
       <c r="H29" s="4"/>
@@ -2486,13 +2512,13 @@
       <c r="D30" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E30" s="18" t="s">
+      <c r="E30" s="17" t="s">
         <v>19</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G30" s="18" t="s">
+      <c r="G30" s="17" t="s">
         <v>30</v>
       </c>
       <c r="H30" s="4"/>
@@ -2508,13 +2534,13 @@
       <c r="D31" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E31" s="18" t="s">
+      <c r="E31" s="17" t="s">
         <v>53</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G31" s="18" t="s">
+      <c r="G31" s="17" t="s">
         <v>32</v>
       </c>
       <c r="H31" s="4"/>
@@ -2530,7 +2556,7 @@
       <c r="D32" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E32" s="18" t="s">
+      <c r="E32" s="17" t="s">
         <v>61</v>
       </c>
       <c r="F32" s="8"/>
@@ -2548,7 +2574,7 @@
       <c r="D33" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E33" s="18" t="s">
+      <c r="E33" s="17" t="s">
         <v>192</v>
       </c>
       <c r="F33" s="4"/>
@@ -2568,7 +2594,7 @@
       <c r="F34" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G34" s="17" t="s">
+      <c r="G34" s="16" t="s">
         <v>35</v>
       </c>
       <c r="H34" s="2"/>
@@ -2586,7 +2612,7 @@
       <c r="F35" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="G35" s="18" t="s">
+      <c r="G35" s="17" t="s">
         <v>43</v>
       </c>
       <c r="H35" s="4"/>
@@ -2599,12 +2625,12 @@
     <row r="36" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4"/>
       <c r="C36" s="5"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="11"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="10"/>
       <c r="F36" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G36" s="18" t="s">
+      <c r="G36" s="17" t="s">
         <v>41</v>
       </c>
       <c r="H36" s="4"/>
@@ -2617,14 +2643,14 @@
     <row r="37" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="4"/>
       <c r="C37" s="5"/>
-      <c r="D37" s="34" t="s">
+      <c r="D37" s="33" t="s">
         <v>204</v>
       </c>
-      <c r="E37" s="35"/>
+      <c r="E37" s="34"/>
       <c r="F37" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G37" s="17" t="s">
+      <c r="G37" s="16" t="s">
         <v>37</v>
       </c>
       <c r="H37" s="2"/>
@@ -2640,13 +2666,13 @@
       <c r="D38" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E38" s="18" t="s">
+      <c r="E38" s="17" t="s">
         <v>59</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G38" s="18" t="s">
+      <c r="G38" s="17" t="s">
         <v>39</v>
       </c>
       <c r="H38" s="4"/>
@@ -2659,16 +2685,16 @@
     <row r="39" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B39" s="4"/>
       <c r="C39" s="5"/>
-      <c r="D39" s="10" t="s">
+      <c r="D39" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="E39" s="25" t="s">
+      <c r="E39" s="24" t="s">
         <v>260</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G39" s="18" t="s">
+      <c r="G39" s="17" t="s">
         <v>15</v>
       </c>
       <c r="H39" s="4"/>
@@ -2686,7 +2712,7 @@
       <c r="F40" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G40" s="18" t="s">
+      <c r="G40" s="17" t="s">
         <v>16</v>
       </c>
       <c r="H40" s="4"/>
@@ -2702,13 +2728,13 @@
       <c r="D41" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E41" s="21" t="s">
+      <c r="E41" s="20" t="s">
         <v>195</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G41" s="18" t="s">
+      <c r="G41" s="17" t="s">
         <v>17</v>
       </c>
       <c r="H41" s="4"/>
@@ -2724,13 +2750,13 @@
       <c r="D42" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E42" s="24" t="s">
+      <c r="E42" s="23" t="s">
         <v>196</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G42" s="18" t="s">
+      <c r="G42" s="17" t="s">
         <v>18</v>
       </c>
       <c r="H42" s="4"/>
@@ -2748,7 +2774,7 @@
       <c r="F43" s="4">
         <v>1</v>
       </c>
-      <c r="G43" s="18" t="s">
+      <c r="G43" s="17" t="s">
         <v>206</v>
       </c>
       <c r="H43" s="4"/>
@@ -2766,7 +2792,7 @@
       <c r="F44" s="4">
         <v>2</v>
       </c>
-      <c r="G44" s="22" t="s">
+      <c r="G44" s="21" t="s">
         <v>207</v>
       </c>
       <c r="H44" s="4"/>
@@ -2783,7 +2809,7 @@
       <c r="F45" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="G45" s="18" t="s">
+      <c r="G45" s="17" t="s">
         <v>55</v>
       </c>
       <c r="H45" s="8"/>
@@ -2794,62 +2820,70 @@
       <c r="M45" s="5"/>
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B46" s="10"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="12" t="s">
+      <c r="B46" s="9"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G46" s="23" t="s">
+      <c r="G46" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H46" s="12"/>
-      <c r="I46" s="11"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="11"/>
-      <c r="L46" s="10"/>
-      <c r="M46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="9"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="9"/>
+      <c r="M46" s="10"/>
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B47" s="10"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="12" t="s">
+      <c r="B47" s="9"/>
+      <c r="C47" s="10"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="G47" s="23" t="s">
+      <c r="G47" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="H47" s="12"/>
-      <c r="I47" s="11"/>
-      <c r="J47" s="10"/>
-      <c r="K47" s="11"/>
-      <c r="L47" s="10"/>
-      <c r="M47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="9"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="9"/>
+      <c r="M47" s="10"/>
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B48" s="10"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="11"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="11"/>
-      <c r="L48" s="10"/>
-      <c r="M48" s="11"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="42" t="s">
+        <v>301</v>
+      </c>
+      <c r="G48" s="22" t="s">
+        <v>303</v>
+      </c>
+      <c r="H48" s="9"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="9"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="9"/>
+      <c r="M48" s="10"/>
     </row>
     <row r="49" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="6"/>
       <c r="C49" s="7"/>
       <c r="D49" s="6"/>
       <c r="E49" s="7"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="7"/>
+      <c r="F49" s="43" t="s">
+        <v>302</v>
+      </c>
+      <c r="G49" s="18" t="s">
+        <v>304</v>
+      </c>
       <c r="H49" s="6"/>
       <c r="I49" s="7"/>
       <c r="J49" s="6"/>
@@ -2897,108 +2931,108 @@
   <sheetData>
     <row r="1" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="35" t="s">
         <v>298</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="38"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="37"/>
     </row>
     <row r="3" spans="2:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="26" t="s">
         <v>242</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="16" t="s">
         <v>220</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="16" t="s">
         <v>267</v>
       </c>
-      <c r="F3" s="27">
+      <c r="F3" s="26">
         <v>6</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="H3" s="30" t="s">
+      <c r="H3" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="I3" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="J3" s="27" t="s">
+      <c r="J3" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="K3" s="17" t="s">
+      <c r="K3" s="16" t="s">
         <v>290</v>
       </c>
-      <c r="L3" s="13" t="s">
+      <c r="L3" s="12" t="s">
         <v>110</v>
       </c>
       <c r="M3" s="3"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="25" t="s">
         <v>243</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="17" t="s">
         <v>267</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="25" t="s">
         <v>231</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="17" t="s">
         <v>270</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="25">
         <v>7</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="17" t="s">
         <v>274</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="H4" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="17" t="s">
         <v>128</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>95</v>
       </c>
       <c r="K4" s="5"/>
-      <c r="L4" s="13" t="s">
+      <c r="L4" s="12" t="s">
         <v>111</v>
       </c>
       <c r="M4" s="3"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="25" t="s">
         <v>244</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="17" t="s">
         <v>266</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="25" t="s">
         <v>254</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="25">
         <v>8</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="17" t="s">
         <v>241</v>
       </c>
       <c r="H5" s="4" t="s">
@@ -3009,124 +3043,124 @@
         <v>96</v>
       </c>
       <c r="K5" s="5"/>
-      <c r="L5" s="14" t="s">
+      <c r="L5" s="13" t="s">
         <v>112</v>
       </c>
       <c r="M5" s="5"/>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="25" t="s">
         <v>245</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="25" t="s">
         <v>229</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="25">
         <v>9</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="17" t="s">
         <v>276</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>86</v>
       </c>
       <c r="I6" s="5"/>
-      <c r="J6" s="26" t="s">
+      <c r="J6" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="K6" s="18" t="s">
+      <c r="K6" s="17" t="s">
         <v>291</v>
       </c>
-      <c r="L6" s="14" t="s">
+      <c r="L6" s="13" t="s">
         <v>113</v>
       </c>
       <c r="M6" s="5"/>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="25" t="s">
         <v>246</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="25" t="s">
         <v>224</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="25">
         <v>0</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="17" t="s">
         <v>277</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>58</v>
       </c>
       <c r="I7" s="5"/>
-      <c r="J7" s="26" t="s">
+      <c r="J7" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="K7" s="18" t="s">
+      <c r="K7" s="17" t="s">
         <v>292</v>
       </c>
-      <c r="L7" s="14" t="s">
+      <c r="L7" s="13" t="s">
         <v>114</v>
       </c>
       <c r="M7" s="5"/>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="25" t="s">
         <v>247</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="17" t="s">
         <v>265</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="25" t="s">
         <v>255</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="17" t="s">
         <v>268</v>
       </c>
-      <c r="F8" s="33" t="s">
+      <c r="F8" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="17" t="s">
         <v>299</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>87</v>
       </c>
       <c r="I8" s="5"/>
-      <c r="J8" s="26" t="s">
+      <c r="J8" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="K8" s="18" t="s">
+      <c r="K8" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="L8" s="14" t="s">
+      <c r="L8" s="13" t="s">
         <v>115</v>
       </c>
       <c r="M8" s="5"/>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="25" t="s">
         <v>248</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="25" t="s">
         <v>256</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="17" t="s">
         <v>219</v>
       </c>
       <c r="F9" s="8" t="s">
@@ -3141,20 +3175,20 @@
         <v>100</v>
       </c>
       <c r="K9" s="5"/>
-      <c r="L9" s="14"/>
+      <c r="L9" s="13"/>
       <c r="M9" s="5"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="25" t="s">
         <v>232</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="25" t="s">
         <v>230</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="17" t="s">
         <v>287</v>
       </c>
       <c r="F10" s="4" t="s">
@@ -3169,10 +3203,10 @@
         <v>101</v>
       </c>
       <c r="K10" s="5"/>
-      <c r="L10" s="28" t="s">
+      <c r="L10" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="M10" s="18" t="s">
+      <c r="M10" s="17" t="s">
         <v>236</v>
       </c>
     </row>
@@ -3181,16 +3215,16 @@
         <v>249</v>
       </c>
       <c r="C11" s="5"/>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="25" t="s">
         <v>257</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="17" t="s">
         <v>288</v>
       </c>
-      <c r="F11" s="26" t="s">
+      <c r="F11" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="G11" s="17" t="s">
         <v>269</v>
       </c>
       <c r="H11" s="4" t="s">
@@ -3201,10 +3235,10 @@
         <v>102</v>
       </c>
       <c r="K11" s="5"/>
-      <c r="L11" s="28" t="s">
+      <c r="L11" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="M11" s="18" t="s">
+      <c r="M11" s="17" t="s">
         <v>237</v>
       </c>
     </row>
@@ -3213,10 +3247,10 @@
         <v>250</v>
       </c>
       <c r="C12" s="5"/>
-      <c r="D12" s="26" t="s">
+      <c r="D12" s="25" t="s">
         <v>233</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="17" t="s">
         <v>216</v>
       </c>
       <c r="F12" s="4" t="s">
@@ -3231,10 +3265,10 @@
         <v>103</v>
       </c>
       <c r="K12" s="5"/>
-      <c r="L12" s="28" t="s">
+      <c r="L12" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="M12" s="18" t="s">
+      <c r="M12" s="17" t="s">
         <v>235</v>
       </c>
     </row>
@@ -3259,10 +3293,10 @@
         <v>104</v>
       </c>
       <c r="K13" s="5"/>
-      <c r="L13" s="28" t="s">
+      <c r="L13" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="M13" s="18" t="s">
+      <c r="M13" s="17" t="s">
         <v>238</v>
       </c>
     </row>
@@ -3271,10 +3305,10 @@
         <v>239</v>
       </c>
       <c r="C14" s="5"/>
-      <c r="D14" s="26">
+      <c r="D14" s="25">
         <v>1</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="17" t="s">
         <v>217</v>
       </c>
       <c r="F14" s="4" t="s">
@@ -3288,10 +3322,10 @@
       <c r="J14" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="K14" s="18" t="s">
+      <c r="K14" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="L14" s="14"/>
+      <c r="L14" s="13"/>
       <c r="M14" s="5"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.25">
@@ -3299,16 +3333,16 @@
         <v>228</v>
       </c>
       <c r="C15" s="5"/>
-      <c r="D15" s="26">
+      <c r="D15" s="25">
         <v>2</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="F15" s="26" t="s">
+      <c r="F15" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="18" t="s">
+      <c r="G15" s="17" t="s">
         <v>199</v>
       </c>
       <c r="H15" s="4" t="s">
@@ -3319,30 +3353,30 @@
         <v>106</v>
       </c>
       <c r="K15" s="5"/>
-      <c r="L15" s="28" t="s">
+      <c r="L15" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="M15" s="18" t="s">
+      <c r="M15" s="17" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="25" t="s">
         <v>252</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="25">
         <v>3</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="17" t="s">
         <v>272</v>
       </c>
-      <c r="F16" s="26" t="s">
+      <c r="F16" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="G16" s="17" t="s">
         <v>21</v>
       </c>
       <c r="H16" s="4" t="s">
@@ -3353,10 +3387,10 @@
         <v>107</v>
       </c>
       <c r="K16" s="5"/>
-      <c r="L16" s="28" t="s">
+      <c r="L16" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="M16" s="18" t="s">
+      <c r="M16" s="17" t="s">
         <v>223</v>
       </c>
     </row>
@@ -3365,52 +3399,52 @@
         <v>253</v>
       </c>
       <c r="C17" s="5"/>
-      <c r="D17" s="26">
+      <c r="D17" s="25">
         <v>4</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="17" t="s">
         <v>273</v>
       </c>
-      <c r="F17" s="26" t="s">
+      <c r="F17" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="G17" s="18" t="s">
+      <c r="G17" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="H17" s="26" t="s">
+      <c r="H17" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="I17" s="18" t="s">
+      <c r="I17" s="17" t="s">
         <v>289</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>108</v>
       </c>
       <c r="K17" s="5"/>
-      <c r="L17" s="28" t="s">
+      <c r="L17" s="27" t="s">
         <v>271</v>
       </c>
-      <c r="M17" s="18" t="s">
+      <c r="M17" s="17" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="18" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="28" t="s">
         <v>240</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="18" t="s">
         <v>297</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="28">
         <v>5</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="F18" s="29" t="s">
+      <c r="F18" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="G18" s="19" t="s">
+      <c r="G18" s="18" t="s">
         <v>262</v>
       </c>
       <c r="H18" s="6" t="s">
@@ -3420,32 +3454,32 @@
       <c r="J18" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="K18" s="19" t="s">
+      <c r="K18" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="L18" s="15"/>
+      <c r="L18" s="14"/>
       <c r="M18" s="7"/>
     </row>
     <row r="19" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="41" t="s">
+      <c r="B20" s="40" t="s">
         <v>278</v>
       </c>
-      <c r="C20" s="42"/>
+      <c r="C20" s="41"/>
     </row>
     <row r="21" spans="2:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="26" t="s">
         <v>279</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="16" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B22" s="26" t="s">
+      <c r="B22" s="25" t="s">
         <v>280</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="17" t="s">
         <v>285</v>
       </c>
     </row>
@@ -3456,42 +3490,42 @@
       <c r="C23" s="5"/>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B24" s="26" t="s">
+      <c r="B24" s="25" t="s">
         <v>293</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="17" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B25" s="26" t="s">
+      <c r="B25" s="25" t="s">
         <v>294</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="17" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B26" s="26" t="s">
+      <c r="B26" s="25" t="s">
         <v>286</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="17" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B27" s="26" t="s">
+      <c r="B27" s="25" t="s">
         <v>230</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="17" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="28" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="29" t="s">
+      <c r="B28" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="18" t="s">
         <v>283</v>
       </c>
     </row>
@@ -3499,21 +3533,21 @@
       <c r="B29" s="1"/>
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="D30" s="20"/>
+      <c r="D30" s="19"/>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B31" s="32"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
-      <c r="J31" s="32"/>
-      <c r="K31" s="32"/>
-      <c r="L31" s="32"/>
-      <c r="M31" s="32"/>
+      <c r="B31" s="31"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31"/>
+      <c r="K31" s="31"/>
+      <c r="L31" s="31"/>
+      <c r="M31" s="31"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B32" s="1"/>
@@ -3522,7 +3556,7 @@
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
-      <c r="H32" s="31"/>
+      <c r="H32" s="30"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -3590,7 +3624,7 @@
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
-      <c r="F37" s="31"/>
+      <c r="F37" s="30"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -3604,7 +3638,7 @@
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
-      <c r="F38" s="31"/>
+      <c r="F38" s="30"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -3658,7 +3692,7 @@
     <row r="42" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
-      <c r="D42" s="31"/>
+      <c r="D42" s="30"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
